--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,37 +680,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128666421</v>
+        <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>91680</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552050</v>
+        <v>552016</v>
       </c>
       <c r="R2" t="n">
-        <v>6842707</v>
+        <v>6842751</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,17 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Helt intill bäcken. Norra sidan.</t>
+          <t>gammal murken tallåga. rotvälta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,61 +783,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128666421</t>
+          <t>https://artportalen.se/Sighting/136921448</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128632785</v>
+        <v>128666421</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552112</v>
+        <v>552050</v>
       </c>
       <c r="R3" t="n">
-        <v>6842733</v>
+        <v>6842707</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,6 +874,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Helt intill bäcken. Norra sidan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,24 +894,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128632785</t>
+          <t>https://artportalen.se/Sighting/128666421</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128668179</v>
+        <v>128632785</v>
       </c>
       <c r="B4" t="n">
         <v>93197</v>
@@ -935,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552097</v>
+        <v>552112</v>
       </c>
       <c r="R4" t="n">
-        <v>6842742</v>
+        <v>6842733</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,11 +995,6 @@
           <t>2025-09-22</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på förmodad kolbotten. tillsammans med knärot.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1007,24 +1008,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128668179</t>
+          <t>https://artportalen.se/Sighting/128632785</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128670325</v>
+        <v>128668179</v>
       </c>
       <c r="B5" t="n">
         <v>93197</v>
@@ -1054,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1070,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552083</v>
+        <v>552097</v>
       </c>
       <c r="R5" t="n">
-        <v>6842727</v>
+        <v>6842742</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1111,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vid förmodad kojruin.Tillsammans med knärot.</t>
+          <t>Växer på förmodad kolbotten. tillsammans med knärot.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,38 +1138,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128670325</t>
+          <t>https://artportalen.se/Sighting/128668179</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128632620</v>
+        <v>128670325</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1178,11 +1179,10 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552066</v>
+        <v>552083</v>
       </c>
       <c r="R6" t="n">
-        <v>6842703</v>
+        <v>6842727</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5 fröställningar från i år</t>
+          <t>Vid förmodad kojruin.Tillsammans med knärot.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,63 +1246,58 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128632620</t>
+          <t>https://artportalen.se/Sighting/128670325</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128633169</v>
+        <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1310,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552087</v>
+        <v>552113</v>
       </c>
       <c r="R7" t="n">
-        <v>6842744</v>
+        <v>6842737</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,19 +1361,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128633169</t>
+          <t>https://artportalen.se/Sighting/136922536</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128666699</v>
+        <v>128632620</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1408,12 +1403,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1425,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552076</v>
+        <v>552066</v>
       </c>
       <c r="R8" t="n">
-        <v>6842720</v>
+        <v>6842703</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ovanlig växtplats, helt intill bäcken, mycket fuktigt.</t>
+          <t>5 fröställningar från i år</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,24 +1476,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128666699</t>
+          <t>https://artportalen.se/Sighting/128632620</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128668071</v>
+        <v>128633169</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1526,8 +1521,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1537,10 +1540,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552097</v>
+        <v>552087</v>
       </c>
       <c r="R9" t="n">
-        <v>6842742</v>
+        <v>6842744</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1575,11 +1578,6 @@
           <t>2025-09-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växtplatsen är en förmodad kolningsplats. Finns tyvärr inte inlagd på Fornsök. Knäroten växer tillsammans med och bland dropptaggsvamp.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1593,24 +1591,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128668071</t>
+          <t>https://artportalen.se/Sighting/128633169</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128669319</v>
+        <v>128666699</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1640,12 +1638,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1657,13 +1655,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552105</v>
+        <v>552076</v>
       </c>
       <c r="R10" t="n">
-        <v>6842738</v>
+        <v>6842720</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1695,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på förmodad kolbotten tillsammans med svart taggsvamp.</t>
+          <t>Ovanlig växtplats, helt intill bäcken, mycket fuktigt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,13 +1722,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128669319</t>
+          <t>https://artportalen.se/Sighting/128666699</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128670372</v>
+        <v>128668071</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1758,16 +1756,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1777,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552083</v>
+        <v>552097</v>
       </c>
       <c r="R11" t="n">
-        <v>6842727</v>
+        <v>6842742</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1817,7 +1807,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Vid förmodad kojruin.</t>
+          <t>Växtplatsen är en förmodad kolningsplats. Finns tyvärr inte inlagd på Fornsök. Knäroten växer tillsammans med och bland dropptaggsvamp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,13 +1834,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128670372</t>
+          <t>https://artportalen.se/Sighting/128668071</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128670766</v>
+        <v>128669319</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1880,7 +1870,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1897,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552010</v>
+        <v>552105</v>
       </c>
       <c r="R12" t="n">
-        <v>6842772</v>
+        <v>6842738</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1935,6 +1925,11 @@
           <t>2025-09-22</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på förmodad kolbotten tillsammans med svart taggsvamp.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1958,6 +1953,241 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669319</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128670372</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552083</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6842727</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Vid förmodad kojruin.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670372</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128670766</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552010</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6842772</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128670766</t>
         </is>
@@ -1976,6 +2206,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49982-2025 artfynd.xlsx
+++ b/artfynd/A 49982-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921448</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136922536</v>
       </c>
       <c r="B7" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
